--- a/Curva Temperatura.xlsx
+++ b/Curva Temperatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\GIT_AULAS_FATEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E126D0F6-9D63-4849-A3DD-A8E0F789513D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6548B4A0-332C-47D0-97BE-CEC04020DE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1D9A3A77-71F0-4909-9ECD-9CA24C7A02A1}"/>
   </bookViews>
@@ -277,88 +277,88 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="28"/>
                 <c:pt idx="0">
-                  <c:v>3.1278560250391201</c:v>
+                  <c:v>3.2167918454935625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.0697138869504537</c:v>
+                  <c:v>3.1876086956521741</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9969140337986775</c:v>
+                  <c:v>3.1502606680826415</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.9076099881093938</c:v>
+                  <c:v>3.1031725888324875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.8004541326067214</c:v>
+                  <c:v>3.0447333772218563</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6749999999999998</c:v>
+                  <c:v>2.9734736842105263</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.3725126475548062</c:v>
+                  <c:v>2.7877807133421402</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>2.6720647773279351</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.0189440993788819</c:v>
+                  <c:v>2.5419354838709678</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.8339848956019547</c:v>
+                  <c:v>2.3987797791981404</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.65</c:v>
+                  <c:v>2.2448979591836733</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4715425531914892</c:v>
+                  <c:v>2.0833385629118291</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.3021794406102432</c:v>
+                  <c:v>1.9174006061686573</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1448275862068964</c:v>
+                  <c:v>1.7508589692369156</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.000989271283266</c:v>
+                  <c:v>1.5869449966865472</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.87138651751545482</c:v>
+                  <c:v>1.4286196911196911</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.75645136426699544</c:v>
+                  <c:v>1.2788897576231428</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.65492144918243023</c:v>
+                  <c:v>1.1386287625418059</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.56640159045725647</c:v>
+                  <c:v>1.0096869462492615</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.48981520906071702</c:v>
+                  <c:v>0.8927363029644575</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.42368168744007667</c:v>
+                  <c:v>0.78744532642151299</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.36666666666666664</c:v>
+                  <c:v>0.69327731092436973</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.31762313601446002</c:v>
+                  <c:v>0.60962705984388554</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.27552928237558427</c:v>
+                  <c:v>0.53578684726430226</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.23945689271405252</c:v>
+                  <c:v>0.47094703049759223</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.20849134377576259</c:v>
+                  <c:v>0.41409645727895211</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.18196832835708074</c:v>
+                  <c:v>0.36450147626618212</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.15911712637770545</c:v>
+                  <c:v>0.32108861829216762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1642,7 +1642,7 @@
         <v>4</v>
       </c>
       <c r="N1" s="3">
-        <v>10000</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D2" s="1">
         <f>((C2*K$1)/(N$1+C2))</f>
-        <v>3.1278560250391236</v>
+        <v>3.2167918454935625</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D3" s="1">
         <f>((C3*K$1)/(N$1+C3))</f>
-        <v>3.0697138869504537</v>
+        <v>3.1876086956521741</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D4" s="1">
         <f t="shared" ref="D4:D29" si="1">((C4*K$1)/(N$1+C4))</f>
-        <v>2.9969140337986775</v>
+        <v>3.1502606680826415</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>8</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D5" s="1">
         <f t="shared" si="1"/>
-        <v>2.9076099881093938</v>
+        <v>3.1031725888324875</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>9</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="D6" s="1">
         <f t="shared" si="1"/>
-        <v>2.8004541326067214</v>
+        <v>3.0447333772218563</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>5</v>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D7" s="1">
         <f t="shared" si="1"/>
-        <v>2.6749999999999998</v>
+        <v>2.9734736842105263</v>
       </c>
       <c r="P7" t="s">
         <v>6</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D8" s="1">
         <f t="shared" si="1"/>
-        <v>2.3725126475548062</v>
+        <v>2.7877807133421402</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
+        <v>2.6720647773279351</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D10" s="1">
         <f t="shared" si="1"/>
-        <v>2.0189440993788819</v>
+        <v>2.5419354838709678</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="1"/>
-        <v>1.8339848956019547</v>
+        <v>2.3987797791981404</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" si="1"/>
-        <v>1.65</v>
+        <v>2.2448979591836733</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="1"/>
-        <v>1.4715425531914892</v>
+        <v>2.0833385629118291</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="1"/>
-        <v>1.3021794406102432</v>
+        <v>1.9174006061686573</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="1"/>
-        <v>1.1448275862068964</v>
+        <v>1.7508589692369156</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" si="1"/>
-        <v>1.000989271283266</v>
+        <v>1.5869449966865472</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="1"/>
-        <v>0.87138651751545482</v>
+        <v>1.4286196911196911</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" si="1"/>
-        <v>0.75645136426699544</v>
+        <v>1.2788897576231428</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="1"/>
-        <v>0.65492144918243023</v>
+        <v>1.1386287625418059</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" si="1"/>
-        <v>0.56640159045725647</v>
+        <v>1.0096869462492615</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" si="1"/>
-        <v>0.48981520906071702</v>
+        <v>0.8927363029644575</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" si="1"/>
-        <v>0.42368168744007667</v>
+        <v>0.78744532642151299</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.69327731092436973</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" si="1"/>
-        <v>0.31762313601446002</v>
+        <v>0.60962705984388554</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D25" s="1">
         <f t="shared" si="1"/>
-        <v>0.27552928237558427</v>
+        <v>0.53578684726430226</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" si="1"/>
-        <v>0.23945689271405252</v>
+        <v>0.47094703049759223</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" si="1"/>
-        <v>0.20849134377576259</v>
+        <v>0.41409645727895211</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" si="1"/>
-        <v>0.18196832835708074</v>
+        <v>0.36450147626618212</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D29" s="1">
         <f t="shared" si="1"/>
-        <v>0.15911712637770545</v>
+        <v>0.32108861829216762</v>
       </c>
     </row>
   </sheetData>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>3.1278560250391201</v>
+        <v>3.2167918454935625</v>
       </c>
       <c r="B2">
         <v>-30</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>3.0697138869504537</v>
+        <v>3.1876086956521741</v>
       </c>
       <c r="B3">
         <v>-25</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>2.9969140337986775</v>
+        <v>3.1502606680826415</v>
       </c>
       <c r="B4">
         <v>-20</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>2.9076099881093938</v>
+        <v>3.1031725888324875</v>
       </c>
       <c r="B5">
         <v>-15</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>2.8004541326067214</v>
+        <v>3.0447333772218563</v>
       </c>
       <c r="B6">
         <v>-10</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>2.6749999999999998</v>
+        <v>2.9734736842105263</v>
       </c>
       <c r="B7">
         <v>-5</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>2.3725126475548062</v>
+        <v>2.7877807133421402</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.6720647773279351</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>2.0189440993788819</v>
+        <v>2.5419354838709678</v>
       </c>
       <c r="B10">
         <v>15</v>
@@ -2217,7 +2217,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>1.8339848956019547</v>
+        <v>2.3987797791981404</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>1.65</v>
+        <v>2.2448979591836733</v>
       </c>
       <c r="B12">
         <v>25</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>1.4715425531914892</v>
+        <v>2.0833385629118291</v>
       </c>
       <c r="B13">
         <v>30</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>1.3021794406102432</v>
+        <v>1.9174006061686573</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>1.1448275862068964</v>
+        <v>1.7508589692369156</v>
       </c>
       <c r="B15">
         <v>40</v>
@@ -2257,7 +2257,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>1.000989271283266</v>
+        <v>1.5869449966865472</v>
       </c>
       <c r="B16">
         <v>45</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>0.87138651751545482</v>
+        <v>1.4286196911196911</v>
       </c>
       <c r="B17">
         <v>50</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>0.75645136426699544</v>
+        <v>1.2788897576231428</v>
       </c>
       <c r="B18">
         <v>55</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>0.65492144918243023</v>
+        <v>1.1386287625418059</v>
       </c>
       <c r="B19">
         <v>60</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>0.56640159045725647</v>
+        <v>1.0096869462492615</v>
       </c>
       <c r="B20">
         <v>65</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>0.48981520906071702</v>
+        <v>0.8927363029644575</v>
       </c>
       <c r="B21">
         <v>70</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>0.42368168744007667</v>
+        <v>0.78744532642151299</v>
       </c>
       <c r="B22">
         <v>75</v>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>0.36666666666666664</v>
+        <v>0.69327731092436973</v>
       </c>
       <c r="B23">
         <v>80</v>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>0.31762313601446002</v>
+        <v>0.60962705984388554</v>
       </c>
       <c r="B24">
         <v>85</v>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>0.27552928237558427</v>
+        <v>0.53578684726430226</v>
       </c>
       <c r="B25">
         <v>90</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>0.23945689271405252</v>
+        <v>0.47094703049759223</v>
       </c>
       <c r="B26">
         <v>95</v>
@@ -2345,7 +2345,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>0.20849134377576259</v>
+        <v>0.41409645727895211</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>0.18196832835708074</v>
+        <v>0.36450147626618212</v>
       </c>
       <c r="B28">
         <v>105</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>0.15911712637770545</v>
+        <v>0.32108861829216762</v>
       </c>
       <c r="B29">
         <v>110</v>
